--- a/site/Active-Directory-Dayforce-UUID-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-Dayforce-UUID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,20 +595,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Global Settings:</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KQS389YFT05Q5TFKJ40BDWY4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-UUID-Integration-Guide/#h_01KQS389YFT05Q5TFKJ40BDWY4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>h_01KQRVKRSZQFS742741S532WEC</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-UUID-Integration-Guide/#h_01KQRVKRSZQFS742741S532WEC</t>
         </is>

--- a/site/Active-Directory-Dayforce-UUID-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-Dayforce-UUID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,42 +595,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Global Settings:</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KQS389YFT05Q5TFKJ40BDWY4</t>
+          <t>h_01KQRVKRSZQFS742741S532WEC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-UUID-Integration-Guide/#h_01KQS389YFT05Q5TFKJ40BDWY4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>h_01KQRVKRSZQFS742741S532WEC</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Dayforce-UUID-Integration-Guide/#h_01KQRVKRSZQFS742741S532WEC</t>
         </is>
